--- a/Excel_Macro/SWW.xlsx
+++ b/Excel_Macro/SWW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\anything-to-share\Excel_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAB19AD-9EF3-4EA9-9B21-35C6D872CB64}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E701D762-0B8F-42A3-82E5-64CCB624E4BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="3435" windowWidth="6420" windowHeight="4515" xr2:uid="{9EDB9979-3425-49AF-9BE8-16DEA303DE4E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>날짜</t>
   </si>
@@ -208,6 +208,58 @@
   </si>
   <si>
     <t>both, 신고가 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지투지바이오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평단가가 6만원, 불타기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업종</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차전지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자사주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전고체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유리기판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이오</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -217,7 +269,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -296,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,6 +376,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,7 +421,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,24 +431,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -421,31 +467,52 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -764,23 +831,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="7"/>
-    <col min="2" max="2" width="16.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="7"/>
-    <col min="4" max="4" width="9.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.625" style="5"/>
-    <col min="9" max="9" width="8.625" style="7"/>
-    <col min="10" max="10" width="19.25" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="5"/>
+    <col min="1" max="1" width="8.625" style="4"/>
+    <col min="2" max="2" width="16.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="4"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="3"/>
+    <col min="10" max="10" width="8.625" style="4"/>
+    <col min="11" max="11" width="19.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -788,588 +856,661 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1">
-        <f>SUM(I2:I26)</f>
+      <c r="J1" s="1">
+        <f>SUM(J2:J26)</f>
         <v>47</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4" t="s">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27">
+        <v>78000</v>
+      </c>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="3" t="s">
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L3" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C4" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="3" t="s">
+      <c r="E4" s="26"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C5" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="3" t="s">
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L5" s="28" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="4" t="s">
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C6" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="19">
+      <c r="E6" s="26">
         <v>46350</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20">
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>47000</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="3" t="s">
+      <c r="I6" s="27"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4" t="s">
+      <c r="L6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C7" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20">
+      <c r="E7" s="26"/>
+      <c r="F7" s="27">
         <v>24000</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4" t="s">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C8" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20">
+      <c r="E8" s="26"/>
+      <c r="F8" s="27">
         <v>164000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="G8" s="27">
         <v>168000</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="3" t="s">
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L8" s="28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="8" t="s">
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C9" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20">
+      <c r="E9" s="26"/>
+      <c r="F9" s="27">
         <v>55000</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="3" t="s">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L9" s="28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="10">
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27">
+        <v>2900</v>
+      </c>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="24">
+        <v>4</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="28"/>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="10">
-        <v>6</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="10">
-        <v>6</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="13">
-        <v>4</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="13">
-        <v>4</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="13">
-        <v>4</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C11" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27">
+        <v>18400</v>
+      </c>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="27"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27">
+        <v>17700</v>
+      </c>
+      <c r="I16" s="27"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="30"/>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="13">
-        <v>4</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="6">
+        <v>6</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26">
-        <v>43500</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="16">
-        <v>3</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="6">
+        <v>6</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="21"/>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="B19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="16">
-        <v>3</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="6">
+        <v>6</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="21"/>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="16">
-        <v>3</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="9">
+        <v>4</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="9">
+        <v>4</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="9">
+        <v>4</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="9">
+        <v>4</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20">
-        <v>2900</v>
-      </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="6">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20">
+        <v>43500</v>
+      </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="I24" s="20"/>
+      <c r="J24" s="12">
+        <v>3</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20">
-        <v>18400</v>
-      </c>
+      <c r="I25" s="20"/>
+      <c r="J25" s="12">
+        <v>3</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="19"/>
       <c r="F26" s="20"/>
-      <c r="G26" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="G26" s="20"/>
       <c r="H26" s="20"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20">
-        <v>17700</v>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="27"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="12">
+        <v>3</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
+  <autoFilter ref="A1:I26" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B10" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
+    <hyperlink ref="B9" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
+    <hyperlink ref="B24" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/Excel_Macro/SWW.xlsx
+++ b/Excel_Macro/SWW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\anything-to-share\Excel_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E701D762-0B8F-42A3-82E5-64CCB624E4BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACD6920-96A1-4066-9E9F-4BAD16268CBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="3435" windowWidth="6420" windowHeight="4515" xr2:uid="{9EDB9979-3425-49AF-9BE8-16DEA303DE4E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
   <si>
     <t>날짜</t>
   </si>
@@ -260,6 +260,35 @@
   </si>
   <si>
     <t>바이오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>리투오</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 생산/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>휴메딕스가 국내 판권을 보유</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -844,7 +873,7 @@
     <col min="9" max="9" width="8.625" style="3"/>
     <col min="10" max="10" width="8.625" style="4"/>
     <col min="11" max="11" width="19.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="8.625" style="3"/>
   </cols>
   <sheetData>
@@ -1147,7 +1176,9 @@
       <c r="I12" s="27"/>
       <c r="J12" s="24"/>
       <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
+      <c r="L12" s="28" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>

--- a/Excel_Macro/SWW.xlsx
+++ b/Excel_Macro/SWW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\anything-to-share\Excel_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACD6920-96A1-4066-9E9F-4BAD16268CBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA31429E-ACFD-4987-B12D-CA65B4756AB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="3435" windowWidth="6420" windowHeight="4515" xr2:uid="{9EDB9979-3425-49AF-9BE8-16DEA303DE4E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
   <si>
     <t>날짜</t>
   </si>
@@ -180,10 +180,6 @@
   </si>
   <si>
     <t>리가켐바이오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -289,6 +285,54 @@
       </rPr>
       <t>휴메딕스가 국내 판권을 보유</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장(삼성에피스홀딩스 전환)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성에피스홀딩스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70만원 이내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 매수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이벡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전량매도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전량매도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀄리타스반도체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반도체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전량매도(교체 목적)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.625" style="4"/>
@@ -885,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -906,50 +950,40 @@
         <v>5</v>
       </c>
       <c r="J1" s="1">
-        <f>SUM(J2:J26)</f>
+        <f>SUM(J6:J30)</f>
         <v>47</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
-      <c r="B2" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>51</v>
-      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="26"/>
       <c r="F2" s="27"/>
-      <c r="G2" s="27">
-        <v>78000</v>
-      </c>
+      <c r="G2" s="27"/>
       <c r="H2" s="27"/>
       <c r="I2" s="27"/>
       <c r="J2" s="24"/>
       <c r="K2" s="28"/>
-      <c r="L2" s="28" t="s">
-        <v>52</v>
-      </c>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="27"/>
@@ -957,23 +991,21 @@
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
       <c r="J3" s="24"/>
-      <c r="K3" s="28" t="s">
-        <v>41</v>
-      </c>
+      <c r="K3" s="28"/>
       <c r="L3" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="25" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="27"/>
@@ -981,132 +1013,124 @@
       <c r="H4" s="27"/>
       <c r="I4" s="27"/>
       <c r="J4" s="24"/>
-      <c r="K4" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="28"/>
+      <c r="L4" s="28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="25" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E5" s="26"/>
-      <c r="F5" s="27"/>
+      <c r="F5" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="G5" s="27"/>
       <c r="H5" s="27"/>
       <c r="I5" s="27"/>
       <c r="J5" s="24"/>
-      <c r="K5" s="28" t="s">
-        <v>41</v>
-      </c>
+      <c r="K5" s="28"/>
       <c r="L5" s="28" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="26">
-        <v>46350</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E6" s="26"/>
       <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27">
-        <v>47000</v>
-      </c>
+      <c r="G6" s="27">
+        <v>78000</v>
+      </c>
+      <c r="H6" s="27"/>
       <c r="I6" s="27"/>
       <c r="J6" s="24"/>
-      <c r="K6" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E7" s="26"/>
-      <c r="F7" s="27">
-        <v>24000</v>
-      </c>
+      <c r="F7" s="27"/>
       <c r="G7" s="27"/>
       <c r="H7" s="27"/>
       <c r="I7" s="27"/>
       <c r="J7" s="24"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="K7" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E8" s="26"/>
-      <c r="F8" s="27">
-        <v>164000</v>
-      </c>
-      <c r="G8" s="27">
-        <v>168000</v>
-      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="27"/>
       <c r="I8" s="27"/>
       <c r="J8" s="24"/>
       <c r="K8" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="L8" s="28"/>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24"/>
-      <c r="B9" s="29" t="s">
-        <v>23</v>
+      <c r="B9" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E9" s="26"/>
-      <c r="F9" s="27">
-        <v>55000</v>
-      </c>
+      <c r="F9" s="27"/>
       <c r="G9" s="27"/>
       <c r="H9" s="27"/>
       <c r="I9" s="27"/>
       <c r="J9" s="24"/>
       <c r="K9" s="28" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>48</v>
@@ -1115,42 +1139,44 @@
     <row r="10" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27">
-        <v>2900</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E10" s="26">
+        <v>46350</v>
+      </c>
+      <c r="F10" s="27"/>
       <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="H10" s="27">
+        <v>47000</v>
+      </c>
       <c r="I10" s="27"/>
-      <c r="J10" s="24">
-        <v>4</v>
-      </c>
+      <c r="J10" s="24"/>
       <c r="K10" s="28" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="L10" s="28"/>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E11" s="26"/>
-      <c r="F11" s="27"/>
+      <c r="F11" s="27">
+        <v>24000</v>
+      </c>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="27"/>
@@ -1161,387 +1187,489 @@
     <row r="12" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="26"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="27">
+        <v>164000</v>
+      </c>
+      <c r="G12" s="27">
+        <v>168000</v>
+      </c>
       <c r="H12" s="27"/>
       <c r="I12" s="27"/>
       <c r="J12" s="24"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="28" t="s">
+        <v>31</v>
+      </c>
       <c r="L12" s="28" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
-      <c r="B13" s="25" t="s">
-        <v>8</v>
+      <c r="B13" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="26"/>
-      <c r="F13" s="27"/>
+      <c r="F13" s="27">
+        <v>55000</v>
+      </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="24"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
+      <c r="K13" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="24"/>
       <c r="B14" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="26"/>
-      <c r="F14" s="27"/>
+      <c r="F14" s="27">
+        <v>2900</v>
+      </c>
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="28"/>
+      <c r="J14" s="24">
+        <v>4</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>17</v>
+      </c>
       <c r="L14" s="28"/>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="27">
-        <v>18400</v>
-      </c>
+      <c r="F15" s="27"/>
       <c r="G15" s="27"/>
-      <c r="H15" s="27" t="s">
-        <v>46</v>
-      </c>
+      <c r="H15" s="27"/>
       <c r="I15" s="27"/>
       <c r="J15" s="24"/>
       <c r="K15" s="28"/>
-      <c r="L15" s="28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="27">
-        <v>17700</v>
-      </c>
+      <c r="H16" s="27"/>
       <c r="I16" s="27"/>
       <c r="J16" s="24"/>
       <c r="K16" s="28"/>
-      <c r="L16" s="30"/>
+      <c r="L16" s="28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27">
+        <v>18400</v>
+      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27">
+        <v>17700</v>
+      </c>
+      <c r="I20" s="27"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="30"/>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C21" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="6">
+        <v>6</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="21"/>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="6">
+        <v>6</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="21"/>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="6">
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="6">
         <v>6</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="21"/>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="L23" s="21"/>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="B24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="6">
-        <v>6</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18" s="21"/>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="9">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D25" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="6">
-        <v>6</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" s="21"/>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="9">
+        <v>4</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="9">
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="9">
         <v>4</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L20" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="L26" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="9">
+      <c r="E27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="9">
         <v>4</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="B28" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20">
+        <v>43500</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="12">
+        <v>3</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="9">
-        <v>4</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="12">
+        <v>3</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="B30" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="9">
-        <v>4</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20">
-        <v>43500</v>
-      </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="12">
+      <c r="D30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="12">
         <v>3</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K30" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="12">
-        <v>3</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="13"/>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="12">
-        <v>3</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="13"/>
+      <c r="L30" s="13" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
+  <autoFilter ref="A1:I30" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
-    <hyperlink ref="B24" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/Excel_Macro/SWW.xlsx
+++ b/Excel_Macro/SWW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sources\anything-to-share\Excel_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA31429E-ACFD-4987-B12D-CA65B4756AB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D29933-F701-4360-86F2-8671E7EC250F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="3435" windowWidth="6420" windowHeight="4515" xr2:uid="{9EDB9979-3425-49AF-9BE8-16DEA303DE4E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
   <si>
     <t>날짜</t>
   </si>
@@ -333,6 +333,18 @@
   </si>
   <si>
     <t>전량매도(교체 목적)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀄리타스반도체에서 교체 매매</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -904,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.625" style="4"/>
@@ -950,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="1">
-        <f>SUM(J6:J30)</f>
+        <f>SUM(J7:J31)</f>
         <v>47</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -977,35 +989,39 @@
     <row r="3" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>72</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
+        <v>76</v>
+      </c>
+      <c r="E3" s="26">
+        <v>43600</v>
+      </c>
+      <c r="F3" s="27">
+        <v>44500</v>
+      </c>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
       <c r="I3" s="27"/>
       <c r="J3" s="24"/>
       <c r="K3" s="28"/>
       <c r="L3" s="28" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="27"/>
@@ -1015,91 +1031,89 @@
       <c r="J4" s="24"/>
       <c r="K4" s="28"/>
       <c r="L4" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E5" s="26"/>
-      <c r="F5" s="27" t="s">
-        <v>65</v>
-      </c>
+      <c r="F5" s="27"/>
       <c r="G5" s="27"/>
       <c r="H5" s="27"/>
       <c r="I5" s="27"/>
       <c r="J5" s="24"/>
       <c r="K5" s="28"/>
       <c r="L5" s="28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E6" s="26"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27">
-        <v>78000</v>
-      </c>
+      <c r="F6" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="27"/>
       <c r="H6" s="27"/>
       <c r="I6" s="27"/>
       <c r="J6" s="24"/>
       <c r="K6" s="28"/>
       <c r="L6" s="28" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="24"/>
       <c r="B7" s="25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="27">
+        <v>78000</v>
+      </c>
       <c r="H7" s="27"/>
       <c r="I7" s="27"/>
       <c r="J7" s="24"/>
-      <c r="K7" s="28" t="s">
-        <v>41</v>
-      </c>
+      <c r="K7" s="28"/>
       <c r="L7" s="28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="27"/>
@@ -1110,12 +1124,14 @@
       <c r="K8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="28"/>
+      <c r="L8" s="28" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>53</v>
@@ -1132,107 +1148,103 @@
       <c r="K9" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="26">
-        <v>46350</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E10" s="26"/>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
-      <c r="H10" s="27">
-        <v>47000</v>
-      </c>
+      <c r="H10" s="27"/>
       <c r="I10" s="27"/>
       <c r="J10" s="24"/>
       <c r="K10" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="28"/>
+        <v>41</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="27">
-        <v>24000</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E11" s="26">
+        <v>46350</v>
+      </c>
+      <c r="F11" s="27"/>
       <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="H11" s="27">
+        <v>47000</v>
+      </c>
       <c r="I11" s="27"/>
       <c r="J11" s="24"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="28" t="s">
+        <v>37</v>
+      </c>
       <c r="L11" s="28"/>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="27">
-        <v>164000</v>
-      </c>
-      <c r="G12" s="27">
-        <v>168000</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="G12" s="27"/>
       <c r="H12" s="27"/>
       <c r="I12" s="27"/>
       <c r="J12" s="24"/>
-      <c r="K12" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="28" t="s">
-        <v>47</v>
-      </c>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
-      <c r="B13" s="29" t="s">
-        <v>23</v>
+      <c r="B13" s="25" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="26"/>
       <c r="F13" s="27">
-        <v>55000</v>
-      </c>
-      <c r="G13" s="27"/>
+        <v>164000</v>
+      </c>
+      <c r="G13" s="27">
+        <v>168000</v>
+      </c>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="24"/>
       <c r="K13" s="28" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L13" s="28" t="s">
         <v>47</v>
@@ -1240,34 +1252,34 @@
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="24"/>
-      <c r="B14" s="25" t="s">
-        <v>11</v>
+      <c r="B14" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="26"/>
       <c r="F14" s="27">
-        <v>2900</v>
+        <v>55000</v>
       </c>
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27"/>
-      <c r="J14" s="24">
-        <v>4</v>
-      </c>
+      <c r="J14" s="24"/>
       <c r="K14" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="28"/>
+        <v>16</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>53</v>
@@ -1276,18 +1288,24 @@
         <v>13</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
+      <c r="F15" s="27">
+        <v>2900</v>
+      </c>
       <c r="G15" s="27"/>
       <c r="H15" s="27"/>
       <c r="I15" s="27"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="28"/>
+      <c r="J15" s="24">
+        <v>4</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>17</v>
+      </c>
       <c r="L15" s="28"/>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>53</v>
@@ -1302,14 +1320,12 @@
       <c r="I16" s="27"/>
       <c r="J16" s="24"/>
       <c r="K16" s="28"/>
-      <c r="L16" s="28" t="s">
-        <v>62</v>
-      </c>
+      <c r="L16" s="28"/>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>53</v>
@@ -1324,12 +1340,14 @@
       <c r="I17" s="27"/>
       <c r="J17" s="24"/>
       <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="L17" s="28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>53</v>
@@ -1349,7 +1367,7 @@
     <row r="19" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>53</v>
@@ -1358,77 +1376,71 @@
         <v>13</v>
       </c>
       <c r="E19" s="26"/>
-      <c r="F19" s="27">
-        <v>18400</v>
-      </c>
+      <c r="F19" s="27"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="27" t="s">
-        <v>45</v>
-      </c>
+      <c r="H19" s="27"/>
       <c r="I19" s="27"/>
       <c r="J19" s="24"/>
       <c r="K19" s="28"/>
-      <c r="L19" s="28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E20" s="26"/>
-      <c r="F20" s="27"/>
+      <c r="F20" s="27">
+        <v>18400</v>
+      </c>
       <c r="G20" s="27"/>
-      <c r="H20" s="27">
-        <v>17700</v>
+      <c r="H20" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="I20" s="27"/>
       <c r="J20" s="24"/>
       <c r="K20" s="28"/>
-      <c r="L20" s="30"/>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="6">
-        <v>6</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="21"/>
+      <c r="L20" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27">
+        <v>17700</v>
+      </c>
+      <c r="I21" s="27"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="30"/>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -1451,10 +1463,10 @@
         <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -1473,42 +1485,40 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="9">
-        <v>4</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="6">
+        <v>6</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="21"/>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>28</v>
@@ -1524,17 +1534,19 @@
       <c r="K25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L25" s="10"/>
+      <c r="L25" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>28</v>
@@ -1550,19 +1562,17 @@
       <c r="K26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L26" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>28</v>
@@ -1578,53 +1588,53 @@
       <c r="K27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L27" s="10"/>
+      <c r="L27" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20">
-        <v>43500</v>
-      </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="12">
-        <v>3</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="B28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="9">
+        <v>4</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>18</v>
+      <c r="B29" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="C29" s="23" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
+      <c r="F29" s="20">
+        <v>43500</v>
+      </c>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
@@ -1634,20 +1644,22 @@
       <c r="K29" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L29" s="13"/>
+      <c r="L29" s="13" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
@@ -1660,16 +1672,42 @@
       <c r="K30" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="12">
+        <v>3</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="13" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I30" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
+  <autoFilter ref="A1:I31" xr:uid="{4A5E97BD-E833-436A-9DAB-57987E36E696}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
-    <hyperlink ref="B28" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{6C65DD6D-8AA5-48E5-B066-DB6D07657F85}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{1C82AF91-0083-48F2-9DDB-1F5621A60CC4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
